--- a/wwwroot/template/TemplateApprover.xlsx
+++ b/wwwroot/template/TemplateApprover.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456A7689-B1D9-4FE0-B3F6-36C5796937F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4B7DB3-A671-4CD1-A61E-AD12B93844E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5880" yWindow="1725" windowWidth="21600" windowHeight="11295" xr2:uid="{8B626CB9-29FE-4B5C-9389-803B2A743CD7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B626CB9-29FE-4B5C-9389-803B2A743CD7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Thuy, VuThiPhuong (BIVN-PUR PUR)</author>
+  </authors>
+  <commentList>
+    <comment ref="Z2" authorId="0" shapeId="0" xr:uid="{72FB8449-6CAF-4ACF-A35E-118641D08BDB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Nếu là hàng tự thiết kế thì copy link bản vẽ</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>No</t>
   </si>
@@ -94,20 +128,12 @@
 </t>
   </si>
   <si>
-    <t>Yêu cầu CO/CQ
-CO/Cqrequirements</t>
-  </si>
-  <si>
     <t>Yêu cầu MSDS kèm số CAS (đối với hóa chất)
 Request MSDS with CAS number (for chemicals)</t>
   </si>
   <si>
     <t>Yêu cầu tiêu chuẩn an toàn
 Request for safety standards</t>
-  </si>
-  <si>
-    <t>File Thiết kế
-Design(*)</t>
   </si>
   <si>
     <t>Nhà Sản xuất
@@ -196,13 +222,43 @@
   </si>
   <si>
     <t>Status quotion request</t>
+  </si>
+  <si>
+    <t>Loại báo giá
+Quotation type</t>
+  </si>
+  <si>
+    <t>Link thiết kế Design link</t>
+  </si>
+  <si>
+    <t>Hình ảnh hàng hóa
+Product images</t>
+  </si>
+  <si>
+    <t>Link BOX</t>
+  </si>
+  <si>
+    <t>Địa điểm nhận hàng
+Delivery Location</t>
+  </si>
+  <si>
+    <t>Người nhận hàng
+Receiver</t>
+  </si>
+  <si>
+    <t>SDT người nhận hàng
+Receiver's Phone Number</t>
+  </si>
+  <si>
+    <t>Yêu cầu CO/CQ
+CO/CQ requirements</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +279,26 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -238,7 +314,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -287,11 +363,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -300,6 +402,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -308,12 +428,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -651,20 +765,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6533764C-5086-42D3-9113-666D7A7B28C0}">
-  <dimension ref="A1:AM3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6533764C-5086-42D3-9113-666D7A7B28C0}">
+  <dimension ref="A1:AS3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="30" width="9.140625" style="3"/>
-    <col min="31" max="31" width="18.42578125" style="3" customWidth="1"/>
-    <col min="32" max="32" width="17.85546875" style="3" customWidth="1"/>
-    <col min="33" max="35" width="9.140625" style="3"/>
-    <col min="36" max="37" width="9.140625" style="3" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="9.140625" style="3"/>
-    <col min="39" max="39" width="13.42578125" style="3" customWidth="1"/>
+    <col min="1" max="22" width="9.140625" style="3"/>
+    <col min="23" max="23" width="11.5703125" style="3" customWidth="1"/>
+    <col min="24" max="25" width="9.140625" style="3"/>
+    <col min="26" max="26" width="11.7109375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="10.85546875" style="3" customWidth="1"/>
+    <col min="28" max="33" width="9.140625" style="3"/>
+    <col min="34" max="34" width="18.42578125" style="3" customWidth="1"/>
+    <col min="35" max="35" width="17.85546875" style="3" customWidth="1"/>
+    <col min="36" max="36" width="9.140625" style="3"/>
+    <col min="37" max="37" width="9.85546875" style="3" customWidth="1"/>
+    <col min="38" max="38" width="11.7109375" style="3" customWidth="1"/>
+    <col min="39" max="39" width="11.42578125" style="3" customWidth="1"/>
+    <col min="40" max="41" width="9.140625" style="3"/>
+    <col min="42" max="43" width="9.140625" style="3" hidden="1" customWidth="1"/>
+    <col min="44" max="44" width="9.140625" style="3"/>
+    <col min="45" max="45" width="13.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -707,275 +830,312 @@
       <c r="N1" s="1">
         <v>14</v>
       </c>
-      <c r="O1" s="5">
-        <f>N1+1</f>
+      <c r="O1" s="1">
         <v>15</v>
       </c>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="1">
+      <c r="P1" s="11">
+        <f>O1+1</f>
         <v>16</v>
       </c>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
       <c r="V1" s="1">
-        <f>U1+1</f>
         <v>17</v>
       </c>
       <c r="W1" s="1">
-        <f t="shared" ref="W1:AM1" si="0">V1+1</f>
+        <f>V1+1</f>
         <v>18</v>
       </c>
       <c r="X1" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="X1:AS1" si="0">W1+1</f>
         <v>19</v>
       </c>
       <c r="Y1" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="Z1" s="1">
-        <f t="shared" si="0"/>
+      <c r="Z1" s="5">
+        <f>Y1+1</f>
         <v>21</v>
       </c>
-      <c r="AA1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="1">
+        <f>Z1+1</f>
         <v>22</v>
       </c>
-      <c r="AB1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AC1" s="1">
         <v>23</v>
       </c>
-      <c r="AC1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AD1" s="1">
+        <f t="shared" ref="AD1" si="1">AB1+1</f>
+        <v>23</v>
+      </c>
+      <c r="AE1" s="1">
         <v>24</v>
       </c>
-      <c r="AD1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AF1" s="1">
+        <f t="shared" ref="AF1" si="2">AD1+1</f>
+        <v>24</v>
+      </c>
+      <c r="AG1" s="1">
         <v>25</v>
       </c>
-      <c r="AE1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AH1" s="1">
+        <f t="shared" ref="AH1" si="3">AF1+1</f>
+        <v>25</v>
+      </c>
+      <c r="AI1" s="1">
         <v>26</v>
       </c>
-      <c r="AF1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AJ1" s="1">
+        <f t="shared" ref="AJ1" si="4">AH1+1</f>
+        <v>26</v>
+      </c>
+      <c r="AK1" s="1">
         <v>27</v>
       </c>
-      <c r="AG1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AL1" s="1">
+        <f t="shared" ref="AL1" si="5">AJ1+1</f>
+        <v>27</v>
+      </c>
+      <c r="AM1" s="1">
         <v>28</v>
       </c>
-      <c r="AH1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AN1" s="1">
+        <f t="shared" ref="AN1" si="6">AL1+1</f>
+        <v>28</v>
+      </c>
+      <c r="AO1" s="1">
         <v>29</v>
       </c>
-      <c r="AI1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AP1" s="1">
+        <f t="shared" ref="AP1" si="7">AN1+1</f>
+        <v>29</v>
+      </c>
+      <c r="AQ1" s="1">
         <v>30</v>
       </c>
-      <c r="AJ1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AR1" s="1">
+        <f t="shared" ref="AR1" si="8">AP1+1</f>
+        <v>30</v>
+      </c>
+      <c r="AS1" s="1">
         <v>31</v>
       </c>
-      <c r="AK1" s="1">
-        <f t="shared" si="0"/>
+    </row>
+    <row r="2" spans="1:45" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="7"/>
+      <c r="AB2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="AR2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AL1" s="1">
-        <f t="shared" si="0"/>
+      <c r="AS2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AM1" s="1">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AH2" s="4" t="s">
+    <row r="3" spans="1:45" ht="115.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AI2" s="4" t="s">
+      <c r="Q3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AJ2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK2" s="4" t="s">
+      <c r="R3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="AL2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AM2" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:39" ht="115.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="4"/>
-      <c r="AG3" s="4"/>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="4"/>
-      <c r="AJ3" s="4"/>
-      <c r="AK3" s="4"/>
-      <c r="AL3" s="9"/>
-      <c r="AM3" s="9"/>
+      <c r="AA3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="7"/>
+      <c r="AL3" s="7"/>
+      <c r="AM3" s="7"/>
+      <c r="AN3" s="10"/>
+      <c r="AO3" s="10"/>
+      <c r="AP3" s="10"/>
+      <c r="AQ3" s="10"/>
+      <c r="AR3" s="13"/>
+      <c r="AS3" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="AL2:AL3"/>
-    <mergeCell ref="AM2:AM3"/>
+  <mergeCells count="41">
+    <mergeCell ref="AR2:AR3"/>
+    <mergeCell ref="AS2:AS3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
     <mergeCell ref="AF2:AF3"/>
     <mergeCell ref="AG2:AG3"/>
     <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AN2:AN3"/>
     <mergeCell ref="X2:X3"/>
     <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="AP2:AP3"/>
+    <mergeCell ref="P1:U1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
@@ -983,20 +1143,27 @@
     <mergeCell ref="L2:L3"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:T2"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="P2:U2"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="AO2:AO3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="AK2:AK3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AQ2:AQ3"/>
+    <mergeCell ref="AE2:AE3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL4:AL572" xr:uid="{14644A99-9082-4B01-8C22-E7F4A3B3E531}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR4:AR572" xr:uid="{14644A99-9082-4B01-8C22-E7F4A3B3E531}">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>